--- a/output/上田確認事項_v01.xlsx
+++ b/output/上田確認事項_v01.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1821,9 +1821,224 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>他社配置</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>上田（分かる範囲）</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>2025年度に他社へ応援を依頼した記録（依頼時刻・回答時刻・回答内容・必要な到着時刻・対応できた時刻）はありますか。</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>試作の「他社配置」では、依頼への対応可否が空欄の船を「未確認」とし、供給可能には数えません。可・不可の根拠が必要です。</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>（本一式に含まれていない）</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>実績で参加していないことを「応援不可」とは扱っていない</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="7" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>供給可能船</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>上田</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>製鉄曳船・西日本海運の船のうち、2025年度に八幡で常駐側として使えた船はどれですか。試作では元帳の記号（T・S・Y・M・P・関・長）を「常駐側の供給数に数える」にしています。</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>正式船名と記号の両方を数えると、同じ船を二重に数えます。対応が分かれば、正式船名の行に切り替えます。</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>試作 マスター F列「常駐側の供給数に数える」</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>正式船名の行（八幡丸など5隻、関豊丸・長豊丸）は「対象外（記号との対応未確認）」と表示</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>出勤手配</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>上田</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>前日に出勤を手配した船が、当日実際に出勤・待機したか（または出勤を取り消したか）の記録はありますか。</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>前日の手配隻数と実作業の隻数のほかに、実際に拘束された乗組員・船を区別するためです。全作業が取り消された日も記録を残します。</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>（本一式に含まれていない）</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>試作の「前日確定」に「実際の出勤・待機」の欄を追加</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>高炉原料</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>上田</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>元帳の品名（鋼材・LNG・鉱石・石炭・支給炭・副原料・内航・その他）のうち、高炉原料にあたるものはどれですか。石炭に発電用など高炉原料以外が含まれるかも教えてください。</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>高炉原料を除いた集計（電炉化後の検討の基礎）を、全作業の集計と別に出すためです。将来どの作業が残るかはAIでは決めません。</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>作業実績R6.4～(バイナリ形式)(3).xlsx シート「R7年度」 Q列（品名）、試作 マスターの品名表</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>初期値：鉱石・石炭＝高炉原料、鋼材・LNG＝高炉原料以外、支給炭・副原料・内航・その他＝未確認（すべて要確認）</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="7" t="n"/>
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>上田</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>品名が「その他」でLNGバース（ZL）の作業（例：12/5 LNG MARS、4/3 REIMEI「LNG補油」）は、LNG入港・出港として扱いますか。</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>LNG入港・出港・警戒を分けて集計するためです。試作では品名が「LNG」の行だけをLNGとして区別しています。</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>作業実績R6.4～(バイナリ形式)(3).xlsx シート「R7年度」 行2082、25～28</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>品名「その他」のため、試作ではLNGに区分されない</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="K6:K34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未回答,回答済み,不明,資料なし"</formula1>
     </dataValidation>
   </dataValidations>
